--- a/output/validation/commission_2024_comparison.xlsx
+++ b/output/validation/commission_2024_comparison.xlsx
@@ -887,22 +887,22 @@
         <v>0.01092449699964959</v>
       </c>
       <c r="K6">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="L6">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="M6">
-        <v>-2.08993</v>
+        <v>-2.04993</v>
       </c>
       <c r="N6">
-        <v>-0.88993</v>
+        <v>-0.87993</v>
       </c>
       <c r="O6" t="s">
         <v>53</v>
       </c>
       <c r="P6">
-        <v>-0.02000000000000002</v>
+        <v>-0.01000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -928,22 +928,22 @@
         <v>-0.5299299999999998</v>
       </c>
       <c r="K7">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L7">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M7">
-        <v>-1.66993</v>
+        <v>-1.59993</v>
       </c>
       <c r="N7">
-        <v>-0.5299299999999998</v>
+        <v>-0.5199299999999998</v>
       </c>
       <c r="O7" t="s">
         <v>53</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.01000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1166,22 +1166,22 @@
         <v>0.001678482873636256</v>
       </c>
       <c r="K12">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="L12">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="M12">
-        <v>0.3499259</v>
+        <v>0.3899259</v>
       </c>
       <c r="N12">
-        <v>0.3499259</v>
+        <v>0.3899259</v>
       </c>
       <c r="O12" t="s">
         <v>53</v>
       </c>
       <c r="P12">
-        <v>-0.04000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1560,28 +1560,28 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="K20">
-        <v>0.9500000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="L20">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="M20">
-        <v>0.8316090000000003</v>
+        <v>0.9116089999999999</v>
       </c>
       <c r="N20">
-        <v>0.8316090000000005</v>
+        <v>0.9116089999999999</v>
       </c>
       <c r="O20" t="s">
         <v>53</v>
       </c>
       <c r="P20">
-        <v>0.0400000000000007</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="Q20">
-        <v>0.04000000000000048</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="R20">
-        <v>0.01000000000000001</v>
+        <v>0.03000000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1987,16 +1987,16 @@
         <v>0.06428754151291116</v>
       </c>
       <c r="K28">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="L28">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="M28">
-        <v>-0.6711990000000001</v>
+        <v>-0.6311990000000001</v>
       </c>
       <c r="N28">
-        <v>-0.6711990000000001</v>
+        <v>-0.6311990000000001</v>
       </c>
       <c r="O28" t="s">
         <v>53</v>
@@ -2172,22 +2172,22 @@
         <v>0.01180647559791481</v>
       </c>
       <c r="K32">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L32">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M32">
-        <v>-1.282466</v>
+        <v>-1.242466</v>
       </c>
       <c r="N32">
-        <v>-0.1424659999999999</v>
+        <v>-0.1324659999999999</v>
       </c>
       <c r="O32" t="s">
         <v>53</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>0.01000000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2257,22 +2257,22 @@
         <v>0.0126600650892712</v>
       </c>
       <c r="K34">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="L34">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="M34">
-        <v>0.2302009</v>
+        <v>0.2702009</v>
       </c>
       <c r="N34">
-        <v>0.2302009</v>
+        <v>0.2702009</v>
       </c>
       <c r="O34" t="s">
         <v>53</v>
       </c>
       <c r="P34">
-        <v>-0.04000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2339,16 +2339,16 @@
         <v>0.0002222812392034257</v>
       </c>
       <c r="K36">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="L36">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="M36">
-        <v>-0.2622969</v>
+        <v>-0.2222969</v>
       </c>
       <c r="N36">
-        <v>-0.2622968999999999</v>
+        <v>-0.2222969</v>
       </c>
       <c r="O36" t="s">
         <v>53</v>
@@ -2374,16 +2374,16 @@
         <v>0.0977031</v>
       </c>
       <c r="K37">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="L37">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="M37">
-        <v>-0.3222969</v>
+        <v>-0.2522969</v>
       </c>
       <c r="N37">
-        <v>-0.3222969</v>
+        <v>-0.2522969</v>
       </c>
       <c r="O37" t="s">
         <v>53</v>
@@ -2421,28 +2421,28 @@
         <v>0.44</v>
       </c>
       <c r="K38">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="L38">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="M38">
-        <v>-1.137243</v>
+        <v>-1.057243</v>
       </c>
       <c r="N38">
-        <v>-0.8676448494267694</v>
+        <v>-0.8674228931928216</v>
       </c>
       <c r="O38" t="s">
         <v>53</v>
       </c>
       <c r="P38">
-        <v>-0.001322112906972928</v>
+        <v>-0.001100156673025099</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>0.02000000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2524,22 +2524,22 @@
         <v>0.0005246665170375309</v>
       </c>
       <c r="K40">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="L40">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="M40">
-        <v>0.03831090000000004</v>
+        <v>0.07831089999999996</v>
       </c>
       <c r="N40">
-        <v>0.03831090000000009</v>
+        <v>0.07831089999999996</v>
       </c>
       <c r="O40" t="s">
         <v>53</v>
       </c>
       <c r="P40">
-        <v>-0.03999999999999987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2615,28 +2615,28 @@
         <v>0.82</v>
       </c>
       <c r="K42">
-        <v>0.8300000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L42">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M42">
-        <v>0.7062990000000005</v>
+        <v>0.746299</v>
       </c>
       <c r="N42">
-        <v>0.7062990000000005</v>
+        <v>0.7462989999999999</v>
       </c>
       <c r="O42" t="s">
         <v>53</v>
       </c>
       <c r="P42">
-        <v>0.04000000000000048</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="Q42">
-        <v>0.04000000000000048</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="R42">
-        <v>0.01000000000000001</v>
+        <v>0.02000000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2668,28 +2668,28 @@
         <v>0.48</v>
       </c>
       <c r="K43">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L43">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="M43">
-        <v>0.746299</v>
+        <v>0.8162989999999999</v>
       </c>
       <c r="N43">
-        <v>1.181673764103333</v>
+        <v>1.182566437820241</v>
       </c>
       <c r="O43" t="s">
         <v>53</v>
       </c>
       <c r="P43">
-        <v>-0.01063061091532536</v>
+        <v>-0.009737937198416979</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>0.01000000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2833,28 +2833,28 @@
         <v>1.22</v>
       </c>
       <c r="K46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="L46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M46">
-        <v>0.5131050000000004</v>
+        <v>0.5531050000000004</v>
       </c>
       <c r="N46">
-        <v>0.5131050000000004</v>
+        <v>0.5531050000000006</v>
       </c>
       <c r="O46" t="s">
         <v>53</v>
       </c>
       <c r="P46">
-        <v>0.04000000000000092</v>
+        <v>0.08000000000000118</v>
       </c>
       <c r="Q46">
-        <v>0.04000000000000004</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="R46">
-        <v>0.01000000000000001</v>
+        <v>0.02000000000000002</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2886,28 +2886,28 @@
         <v>0.74</v>
       </c>
       <c r="K47">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="L47">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="M47">
-        <v>0.7731050000000002</v>
+        <v>0.8431050000000004</v>
       </c>
       <c r="N47">
-        <v>0.773105000000001</v>
+        <v>0.8431050000000004</v>
       </c>
       <c r="O47" t="s">
         <v>53</v>
       </c>
       <c r="P47">
-        <v>-0.002899756026627287</v>
+        <v>0.06710024397337211</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>0.01000000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -3263,22 +3263,22 @@
         <v>0.01255560204561235</v>
       </c>
       <c r="K54">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="L54">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="M54">
-        <v>-1.7872208</v>
+        <v>-1.7472208</v>
       </c>
       <c r="N54">
-        <v>-0.7672207999999999</v>
+        <v>-0.7372207999999999</v>
       </c>
       <c r="O54" t="s">
         <v>53</v>
       </c>
       <c r="P54">
-        <v>0.06000000000000005</v>
+        <v>0.09000000000000008</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -3304,22 +3304,22 @@
         <v>-0.8472207999999998</v>
       </c>
       <c r="K55">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="L55">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="M55">
-        <v>-1.8972208</v>
+        <v>-1.8272208</v>
       </c>
       <c r="N55">
-        <v>-0.6572207999999999</v>
+        <v>-1.2172208</v>
       </c>
       <c r="O55" t="s">
         <v>53</v>
       </c>
       <c r="P55">
-        <v>0.1899999999999998</v>
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
